--- a/schools.xlsx
+++ b/schools.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="21029"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\codo\zeequeMagazin\frontend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B9A5024-A2BC-4F95-9314-732E59995006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53675B2-4AA1-475C-9778-AD39A15E7737}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8928" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -18,25 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$1:$H$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" forceFullCalc="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="520">
   <si>
     <t>SL.NO</t>
   </si>
@@ -107,9 +94,6 @@
     <t>Zeequepoonoor@gmail.com</t>
   </si>
   <si>
-    <t>NO</t>
-  </si>
-  <si>
     <t>ZQC16/005</t>
   </si>
   <si>
@@ -1581,13 +1565,31 @@
   </si>
   <si>
     <t>badriyyazeeque@gmail.com</t>
+  </si>
+  <si>
+    <t>Zahracampus1@gmail.com</t>
+  </si>
+  <si>
+    <t>zq.gardenvalley1@gmail.com</t>
+  </si>
+  <si>
+    <t>11111@gmail.com</t>
+  </si>
+  <si>
+    <t>2222@gmail.com</t>
+  </si>
+  <si>
+    <t>3333@gmail.com</t>
+  </si>
+  <si>
+    <t>4444@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1597,6 +1599,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1617,14 +1625,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1928,14 +1939,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H122"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="61.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="37.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1961,7 +1972,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1987,7 +1998,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2013,7 +2024,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2039,18 +2050,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
@@ -2062,21 +2073,21 @@
         <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>29</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
       </c>
       <c r="E6" t="s">
         <v>11</v>
@@ -2088,21 +2099,21 @@
         <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
       </c>
       <c r="E7" t="s">
         <v>11</v>
@@ -2114,21 +2125,21 @@
         <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
         <v>36</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
       </c>
       <c r="E8" t="s">
         <v>11</v>
@@ -2140,21 +2151,21 @@
         <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
         <v>40</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
@@ -2166,21 +2177,21 @@
         <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
         <v>44</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>45</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
       </c>
       <c r="E10" t="s">
         <v>11</v>
@@ -2192,21 +2203,21 @@
         <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" t="s">
         <v>48</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>49</v>
-      </c>
-      <c r="D11" t="s">
-        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -2218,21 +2229,21 @@
         <v>13</v>
       </c>
       <c r="H11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
         <v>52</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>53</v>
-      </c>
-      <c r="D12" t="s">
-        <v>54</v>
       </c>
       <c r="E12" t="s">
         <v>11</v>
@@ -2244,21 +2255,21 @@
         <v>13</v>
       </c>
       <c r="H12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>56</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>57</v>
-      </c>
-      <c r="D13" t="s">
-        <v>58</v>
       </c>
       <c r="E13" t="s">
         <v>11</v>
@@ -2270,778 +2281,778 @@
         <v>13</v>
       </c>
       <c r="H13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" t="s">
         <v>63</v>
       </c>
-      <c r="E14" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H14" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
         <v>65</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>66</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15" t="s">
         <v>67</v>
       </c>
-      <c r="E15" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s">
         <v>69</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>70</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" t="s">
         <v>71</v>
       </c>
-      <c r="E16" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H16" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" t="s">
         <v>73</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>74</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
+        <v>59</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" t="s">
         <v>75</v>
       </c>
-      <c r="E17" t="s">
-        <v>60</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
         <v>77</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>78</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" t="s">
         <v>79</v>
       </c>
-      <c r="E18" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" t="s">
         <v>81</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>82</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>83</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" t="s">
         <v>84</v>
       </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" t="s">
-        <v>13</v>
-      </c>
-      <c r="H19" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C20" t="s">
         <v>86</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>87</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
+        <v>83</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" t="s">
         <v>88</v>
       </c>
-      <c r="E20" t="s">
-        <v>84</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" t="s">
         <v>90</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>91</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" t="s">
         <v>92</v>
       </c>
-      <c r="E21" t="s">
-        <v>84</v>
-      </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" t="s">
         <v>94</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>95</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" t="s">
         <v>96</v>
       </c>
-      <c r="E22" t="s">
-        <v>84</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" t="s">
         <v>98</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>99</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" t="s">
         <v>100</v>
       </c>
-      <c r="E23" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" t="s">
-        <v>13</v>
-      </c>
-      <c r="H23" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" t="s">
         <v>102</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>103</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" t="s">
         <v>104</v>
       </c>
-      <c r="E24" t="s">
-        <v>84</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" t="s">
         <v>108</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>109</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
+        <v>83</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" t="s">
         <v>110</v>
       </c>
-      <c r="E25" t="s">
-        <v>84</v>
-      </c>
-      <c r="F25" t="s">
-        <v>12</v>
-      </c>
-      <c r="G25" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C26" t="s">
         <v>114</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" t="s">
         <v>115</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26" t="s">
         <v>117</v>
       </c>
-      <c r="E26" t="s">
-        <v>116</v>
-      </c>
-      <c r="F26" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" t="s">
         <v>119</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>120</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
         <v>121</v>
       </c>
-      <c r="E27" t="s">
-        <v>60</v>
-      </c>
-      <c r="F27" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" t="s">
-        <v>13</v>
-      </c>
-      <c r="H27" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" t="s">
         <v>123</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>124</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28" t="s">
         <v>125</v>
       </c>
-      <c r="E28" t="s">
-        <v>116</v>
-      </c>
-      <c r="F28" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" t="s">
-        <v>13</v>
-      </c>
-      <c r="H28" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" t="s">
         <v>127</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>128</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
+        <v>59</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" t="s">
         <v>129</v>
       </c>
-      <c r="E29" t="s">
-        <v>60</v>
-      </c>
-      <c r="F29" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" t="s">
-        <v>13</v>
-      </c>
-      <c r="H29" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" t="s">
         <v>132</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>133</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
+        <v>59</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30" t="s">
         <v>134</v>
       </c>
-      <c r="E30" t="s">
-        <v>60</v>
-      </c>
-      <c r="F30" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" t="s">
-        <v>13</v>
-      </c>
-      <c r="H30" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" t="s">
         <v>137</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>138</v>
       </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
+        <v>135</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" t="s">
         <v>139</v>
       </c>
-      <c r="E31" t="s">
-        <v>136</v>
-      </c>
-      <c r="F31" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32" t="s">
         <v>141</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>142</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
+        <v>83</v>
+      </c>
+      <c r="F32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" t="s">
         <v>143</v>
       </c>
-      <c r="E32" t="s">
-        <v>84</v>
-      </c>
-      <c r="F32" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H32" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>144</v>
+      </c>
+      <c r="C33" t="s">
         <v>145</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>146</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+      <c r="H33" t="s">
         <v>147</v>
       </c>
-      <c r="E33" t="s">
-        <v>84</v>
-      </c>
-      <c r="F33" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33" t="s">
-        <v>13</v>
-      </c>
-      <c r="H33" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>148</v>
+      </c>
+      <c r="C34" t="s">
         <v>149</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>150</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
+        <v>83</v>
+      </c>
+      <c r="F34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+      <c r="H34" t="s">
         <v>151</v>
       </c>
-      <c r="E34" t="s">
-        <v>84</v>
-      </c>
-      <c r="F34" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>152</v>
+      </c>
+      <c r="C35" t="s">
         <v>153</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>154</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
+        <v>83</v>
+      </c>
+      <c r="F35" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" t="s">
         <v>155</v>
       </c>
-      <c r="E35" t="s">
-        <v>84</v>
-      </c>
-      <c r="F35" t="s">
-        <v>12</v>
-      </c>
-      <c r="G35" t="s">
-        <v>13</v>
-      </c>
-      <c r="H35" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>156</v>
+      </c>
+      <c r="C36" t="s">
         <v>157</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>158</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
+        <v>115</v>
+      </c>
+      <c r="F36" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" t="s">
+        <v>13</v>
+      </c>
+      <c r="H36" t="s">
         <v>159</v>
       </c>
-      <c r="E36" t="s">
-        <v>116</v>
-      </c>
-      <c r="F36" t="s">
-        <v>12</v>
-      </c>
-      <c r="G36" t="s">
-        <v>13</v>
-      </c>
-      <c r="H36" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>160</v>
+      </c>
+      <c r="C37" t="s">
         <v>161</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>162</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>163</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" t="s">
+        <v>13</v>
+      </c>
+      <c r="H37" t="s">
         <v>164</v>
       </c>
-      <c r="F37" t="s">
-        <v>12</v>
-      </c>
-      <c r="G37" t="s">
-        <v>13</v>
-      </c>
-      <c r="H37" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>165</v>
+      </c>
+      <c r="C38" t="s">
         <v>166</v>
       </c>
-      <c r="C38" t="s">
+      <c r="D38" t="s">
         <v>167</v>
       </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
+        <v>83</v>
+      </c>
+      <c r="F38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" t="s">
+        <v>13</v>
+      </c>
+      <c r="H38" t="s">
         <v>168</v>
       </c>
-      <c r="E38" t="s">
-        <v>84</v>
-      </c>
-      <c r="F38" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38" t="s">
-        <v>13</v>
-      </c>
-      <c r="H38" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C39" t="s">
         <v>170</v>
       </c>
-      <c r="C39" t="s">
+      <c r="D39" t="s">
+        <v>172</v>
+      </c>
+      <c r="E39" t="s">
         <v>171</v>
       </c>
-      <c r="D39" t="s">
+      <c r="F39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" t="s">
         <v>173</v>
       </c>
-      <c r="E39" t="s">
-        <v>172</v>
-      </c>
-      <c r="F39" t="s">
-        <v>12</v>
-      </c>
-      <c r="G39" t="s">
-        <v>13</v>
-      </c>
-      <c r="H39" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>174</v>
+      </c>
+      <c r="C40" t="s">
         <v>175</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>176</v>
       </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
+        <v>105</v>
+      </c>
+      <c r="F40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" t="s">
+        <v>13</v>
+      </c>
+      <c r="H40" t="s">
         <v>177</v>
       </c>
-      <c r="E40" t="s">
-        <v>106</v>
-      </c>
-      <c r="F40" t="s">
-        <v>12</v>
-      </c>
-      <c r="G40" t="s">
-        <v>13</v>
-      </c>
-      <c r="H40" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
+        <v>178</v>
+      </c>
+      <c r="C41" t="s">
         <v>179</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>180</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
+        <v>83</v>
+      </c>
+      <c r="F41" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H41" t="s">
         <v>181</v>
       </c>
-      <c r="E41" t="s">
-        <v>84</v>
-      </c>
-      <c r="F41" t="s">
-        <v>12</v>
-      </c>
-      <c r="G41" t="s">
-        <v>13</v>
-      </c>
-      <c r="H41" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
+        <v>182</v>
+      </c>
+      <c r="C42" t="s">
         <v>183</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>184</v>
       </c>
-      <c r="D42" t="s">
+      <c r="E42" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" t="s">
+        <v>12</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+      <c r="H42" t="s">
         <v>185</v>
       </c>
-      <c r="E42" t="s">
-        <v>84</v>
-      </c>
-      <c r="F42" t="s">
-        <v>12</v>
-      </c>
-      <c r="G42" t="s">
-        <v>13</v>
-      </c>
-      <c r="H42" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
+        <v>186</v>
+      </c>
+      <c r="C43" t="s">
         <v>187</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>188</v>
       </c>
-      <c r="D43" t="s">
-        <v>189</v>
-      </c>
       <c r="E43" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F43" t="s">
         <v>12</v>
@@ -3049,100 +3060,100 @@
       <c r="G43" t="s">
         <v>13</v>
       </c>
-      <c r="H43" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H43" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>189</v>
+      </c>
+      <c r="C44" t="s">
         <v>190</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="s">
         <v>191</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
+        <v>111</v>
+      </c>
+      <c r="F44" t="s">
+        <v>112</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+      <c r="H44" t="s">
         <v>192</v>
       </c>
-      <c r="E44" t="s">
-        <v>112</v>
-      </c>
-      <c r="F44" t="s">
-        <v>113</v>
-      </c>
-      <c r="G44" t="s">
-        <v>13</v>
-      </c>
-      <c r="H44" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
+        <v>193</v>
+      </c>
+      <c r="C45" t="s">
         <v>194</v>
       </c>
-      <c r="C45" t="s">
+      <c r="D45" t="s">
         <v>195</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
+        <v>83</v>
+      </c>
+      <c r="F45" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" t="s">
         <v>196</v>
       </c>
-      <c r="E45" t="s">
-        <v>84</v>
-      </c>
-      <c r="F45" t="s">
-        <v>12</v>
-      </c>
-      <c r="G45" t="s">
-        <v>13</v>
-      </c>
-      <c r="H45" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>197</v>
+      </c>
+      <c r="C46" t="s">
         <v>198</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>199</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
+        <v>171</v>
+      </c>
+      <c r="F46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" t="s">
         <v>200</v>
       </c>
-      <c r="E46" t="s">
-        <v>172</v>
-      </c>
-      <c r="F46" t="s">
-        <v>12</v>
-      </c>
-      <c r="G46" t="s">
-        <v>13</v>
-      </c>
-      <c r="H46" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>201</v>
+      </c>
+      <c r="C47" t="s">
         <v>202</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>203</v>
-      </c>
-      <c r="D47" t="s">
-        <v>204</v>
       </c>
       <c r="E47" t="s">
         <v>11</v>
@@ -3154,746 +3165,749 @@
         <v>13</v>
       </c>
       <c r="H47" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>205</v>
+      </c>
+      <c r="C48" t="s">
         <v>206</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>207</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
+        <v>59</v>
+      </c>
+      <c r="F48" t="s">
+        <v>12</v>
+      </c>
+      <c r="G48" t="s">
+        <v>13</v>
+      </c>
+      <c r="H48" t="s">
         <v>208</v>
       </c>
-      <c r="E48" t="s">
-        <v>60</v>
-      </c>
-      <c r="F48" t="s">
-        <v>12</v>
-      </c>
-      <c r="G48" t="s">
-        <v>13</v>
-      </c>
-      <c r="H48" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>209</v>
+      </c>
+      <c r="C49" t="s">
         <v>210</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>211</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
+        <v>111</v>
+      </c>
+      <c r="F49" t="s">
+        <v>112</v>
+      </c>
+      <c r="G49" t="s">
+        <v>13</v>
+      </c>
+      <c r="H49" t="s">
         <v>212</v>
       </c>
-      <c r="E49" t="s">
-        <v>112</v>
-      </c>
-      <c r="F49" t="s">
-        <v>113</v>
-      </c>
-      <c r="G49" t="s">
-        <v>13</v>
-      </c>
-      <c r="H49" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
+        <v>213</v>
+      </c>
+      <c r="C50" t="s">
         <v>214</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>215</v>
       </c>
-      <c r="D50" t="s">
+      <c r="E50" t="s">
+        <v>111</v>
+      </c>
+      <c r="F50" t="s">
+        <v>112</v>
+      </c>
+      <c r="G50" t="s">
+        <v>13</v>
+      </c>
+      <c r="H50" t="s">
         <v>216</v>
       </c>
-      <c r="E50" t="s">
-        <v>112</v>
-      </c>
-      <c r="F50" t="s">
-        <v>113</v>
-      </c>
-      <c r="G50" t="s">
-        <v>13</v>
-      </c>
-      <c r="H50" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>217</v>
+      </c>
+      <c r="C51" t="s">
         <v>218</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>219</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
+        <v>59</v>
+      </c>
+      <c r="F51" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" t="s">
+        <v>13</v>
+      </c>
+      <c r="H51" t="s">
         <v>220</v>
       </c>
-      <c r="E51" t="s">
-        <v>60</v>
-      </c>
-      <c r="F51" t="s">
-        <v>12</v>
-      </c>
-      <c r="G51" t="s">
-        <v>13</v>
-      </c>
-      <c r="H51" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>221</v>
+      </c>
+      <c r="C52" t="s">
         <v>222</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>223</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
+        <v>163</v>
+      </c>
+      <c r="F52" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" t="s">
+        <v>13</v>
+      </c>
+      <c r="H52" t="s">
         <v>224</v>
       </c>
-      <c r="E52" t="s">
-        <v>164</v>
-      </c>
-      <c r="F52" t="s">
-        <v>12</v>
-      </c>
-      <c r="G52" t="s">
-        <v>13</v>
-      </c>
-      <c r="H52" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>225</v>
+      </c>
+      <c r="C53" t="s">
         <v>226</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>227</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>228</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
+        <v>112</v>
+      </c>
+      <c r="G53" t="s">
+        <v>13</v>
+      </c>
+      <c r="H53" t="s">
         <v>229</v>
       </c>
-      <c r="F53" t="s">
-        <v>113</v>
-      </c>
-      <c r="G53" t="s">
-        <v>13</v>
-      </c>
-      <c r="H53" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>230</v>
+      </c>
+      <c r="C54" t="s">
         <v>231</v>
       </c>
-      <c r="C54" t="s">
+      <c r="D54" t="s">
         <v>232</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
+        <v>163</v>
+      </c>
+      <c r="F54" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" t="s">
         <v>233</v>
       </c>
-      <c r="E54" t="s">
-        <v>164</v>
-      </c>
-      <c r="F54" t="s">
-        <v>12</v>
-      </c>
-      <c r="G54" t="s">
-        <v>13</v>
-      </c>
-      <c r="H54" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>234</v>
+      </c>
+      <c r="C55" t="s">
         <v>235</v>
       </c>
-      <c r="C55" t="s">
+      <c r="D55" t="s">
         <v>236</v>
       </c>
-      <c r="D55" t="s">
+      <c r="E55" t="s">
+        <v>111</v>
+      </c>
+      <c r="F55" t="s">
+        <v>112</v>
+      </c>
+      <c r="G55" t="s">
+        <v>13</v>
+      </c>
+      <c r="H55" t="s">
         <v>237</v>
       </c>
-      <c r="E55" t="s">
-        <v>112</v>
-      </c>
-      <c r="F55" t="s">
-        <v>113</v>
-      </c>
-      <c r="G55" t="s">
-        <v>13</v>
-      </c>
-      <c r="H55" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>238</v>
+      </c>
+      <c r="C56" t="s">
         <v>239</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>240</v>
       </c>
-      <c r="D56" t="s">
+      <c r="E56" t="s">
+        <v>83</v>
+      </c>
+      <c r="F56" t="s">
+        <v>12</v>
+      </c>
+      <c r="G56" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" t="s">
         <v>241</v>
       </c>
-      <c r="E56" t="s">
-        <v>84</v>
-      </c>
-      <c r="F56" t="s">
-        <v>12</v>
-      </c>
-      <c r="G56" t="s">
-        <v>13</v>
-      </c>
-      <c r="H56" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>242</v>
+      </c>
+      <c r="C57" t="s">
         <v>243</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>244</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
+        <v>83</v>
+      </c>
+      <c r="F57" t="s">
+        <v>12</v>
+      </c>
+      <c r="G57" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" t="s">
         <v>245</v>
       </c>
-      <c r="E57" t="s">
-        <v>84</v>
-      </c>
-      <c r="F57" t="s">
-        <v>12</v>
-      </c>
-      <c r="G57" t="s">
-        <v>13</v>
-      </c>
-      <c r="H57" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>246</v>
+      </c>
+      <c r="C58" t="s">
         <v>247</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>248</v>
       </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
+        <v>105</v>
+      </c>
+      <c r="F58" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58" t="s">
+        <v>13</v>
+      </c>
+      <c r="H58" t="s">
         <v>249</v>
       </c>
-      <c r="E58" t="s">
-        <v>106</v>
-      </c>
-      <c r="F58" t="s">
-        <v>12</v>
-      </c>
-      <c r="G58" t="s">
-        <v>13</v>
-      </c>
-      <c r="H58" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
+        <v>250</v>
+      </c>
+      <c r="C59" t="s">
         <v>251</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
         <v>252</v>
       </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
+        <v>106</v>
+      </c>
+      <c r="F59" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" t="s">
+        <v>13</v>
+      </c>
+      <c r="H59" t="s">
         <v>253</v>
       </c>
-      <c r="E59" t="s">
-        <v>107</v>
-      </c>
-      <c r="F59" t="s">
-        <v>12</v>
-      </c>
-      <c r="G59" t="s">
-        <v>13</v>
-      </c>
-      <c r="H59" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>254</v>
+      </c>
+      <c r="C60" t="s">
         <v>255</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
         <v>256</v>
       </c>
-      <c r="D60" t="s">
+      <c r="E60" t="s">
+        <v>105</v>
+      </c>
+      <c r="F60" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" t="s">
+        <v>13</v>
+      </c>
+      <c r="H60" t="s">
         <v>257</v>
       </c>
-      <c r="E60" t="s">
-        <v>106</v>
-      </c>
-      <c r="F60" t="s">
-        <v>12</v>
-      </c>
-      <c r="G60" t="s">
-        <v>13</v>
-      </c>
-      <c r="H60" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>258</v>
+      </c>
+      <c r="C61" t="s">
         <v>259</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>260</v>
       </c>
-      <c r="D61" t="s">
+      <c r="E61" t="s">
+        <v>135</v>
+      </c>
+      <c r="F61" t="s">
+        <v>12</v>
+      </c>
+      <c r="G61" t="s">
+        <v>13</v>
+      </c>
+      <c r="H61" t="s">
         <v>261</v>
       </c>
-      <c r="E61" t="s">
-        <v>136</v>
-      </c>
-      <c r="F61" t="s">
-        <v>12</v>
-      </c>
-      <c r="G61" t="s">
-        <v>13</v>
-      </c>
-      <c r="H61" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
+        <v>262</v>
+      </c>
+      <c r="C62" t="s">
         <v>263</v>
       </c>
-      <c r="C62" t="s">
+      <c r="D62" t="s">
         <v>264</v>
       </c>
-      <c r="D62" t="s">
+      <c r="E62" t="s">
+        <v>111</v>
+      </c>
+      <c r="F62" t="s">
+        <v>112</v>
+      </c>
+      <c r="G62" t="s">
+        <v>13</v>
+      </c>
+      <c r="H62" t="s">
         <v>265</v>
       </c>
-      <c r="E62" t="s">
-        <v>112</v>
-      </c>
-      <c r="F62" t="s">
-        <v>113</v>
-      </c>
-      <c r="G62" t="s">
-        <v>13</v>
-      </c>
-      <c r="H62" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>270</v>
+      </c>
+      <c r="C63" t="s">
         <v>271</v>
       </c>
-      <c r="C63" t="s">
+      <c r="D63" t="s">
         <v>272</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>273</v>
       </c>
-      <c r="E63" t="s">
+      <c r="F63" t="s">
+        <v>112</v>
+      </c>
+      <c r="G63" t="s">
+        <v>13</v>
+      </c>
+      <c r="H63" t="s">
         <v>274</v>
       </c>
-      <c r="F63" t="s">
-        <v>113</v>
-      </c>
-      <c r="G63" t="s">
-        <v>13</v>
-      </c>
-      <c r="H63" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
+        <v>266</v>
+      </c>
+      <c r="C64" t="s">
         <v>267</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>268</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
+        <v>105</v>
+      </c>
+      <c r="F64" t="s">
+        <v>12</v>
+      </c>
+      <c r="G64" t="s">
+        <v>13</v>
+      </c>
+      <c r="H64" t="s">
         <v>269</v>
       </c>
-      <c r="E64" t="s">
-        <v>106</v>
-      </c>
-      <c r="F64" t="s">
-        <v>12</v>
-      </c>
-      <c r="G64" t="s">
-        <v>13</v>
-      </c>
-      <c r="H64" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
+        <v>275</v>
+      </c>
+      <c r="C65" t="s">
         <v>276</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>277</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
+        <v>115</v>
+      </c>
+      <c r="F65" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65" t="s">
+        <v>13</v>
+      </c>
+      <c r="H65" t="s">
         <v>278</v>
       </c>
-      <c r="E65" t="s">
-        <v>116</v>
-      </c>
-      <c r="F65" t="s">
-        <v>12</v>
-      </c>
-      <c r="G65" t="s">
-        <v>13</v>
-      </c>
-      <c r="H65" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
+        <v>280</v>
+      </c>
+      <c r="C66" t="s">
         <v>281</v>
       </c>
-      <c r="C66" t="s">
+      <c r="D66" t="s">
         <v>282</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
+        <v>135</v>
+      </c>
+      <c r="F66" t="s">
+        <v>12</v>
+      </c>
+      <c r="G66" t="s">
+        <v>13</v>
+      </c>
+      <c r="H66" t="s">
         <v>283</v>
       </c>
-      <c r="E66" t="s">
-        <v>136</v>
-      </c>
-      <c r="F66" t="s">
-        <v>12</v>
-      </c>
-      <c r="G66" t="s">
-        <v>13</v>
-      </c>
-      <c r="H66" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>284</v>
+      </c>
+      <c r="C67" t="s">
         <v>285</v>
       </c>
-      <c r="C67" t="s">
+      <c r="D67" t="s">
         <v>286</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
+        <v>130</v>
+      </c>
+      <c r="F67" t="s">
+        <v>12</v>
+      </c>
+      <c r="G67" t="s">
+        <v>13</v>
+      </c>
+      <c r="H67" t="s">
         <v>287</v>
       </c>
-      <c r="E67" t="s">
-        <v>131</v>
-      </c>
-      <c r="F67" t="s">
-        <v>12</v>
-      </c>
-      <c r="G67" t="s">
-        <v>13</v>
-      </c>
-      <c r="H67" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>288</v>
+      </c>
+      <c r="C68" t="s">
         <v>289</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>290</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>291</v>
       </c>
-      <c r="E68" t="s">
+      <c r="F68" t="s">
+        <v>112</v>
+      </c>
+      <c r="G68" t="s">
+        <v>13</v>
+      </c>
+      <c r="H68" t="s">
         <v>292</v>
       </c>
-      <c r="F68" t="s">
-        <v>113</v>
-      </c>
-      <c r="G68" t="s">
-        <v>13</v>
-      </c>
-      <c r="H68" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>293</v>
+      </c>
+      <c r="C69" t="s">
         <v>294</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>295</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
+        <v>111</v>
+      </c>
+      <c r="F69" t="s">
+        <v>112</v>
+      </c>
+      <c r="G69" t="s">
+        <v>13</v>
+      </c>
+      <c r="H69" t="s">
         <v>296</v>
       </c>
-      <c r="E69" t="s">
-        <v>112</v>
-      </c>
-      <c r="F69" t="s">
-        <v>113</v>
-      </c>
-      <c r="G69" t="s">
-        <v>13</v>
-      </c>
-      <c r="H69" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
+        <v>297</v>
+      </c>
+      <c r="C70" t="s">
         <v>298</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>299</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
+        <v>111</v>
+      </c>
+      <c r="F70" t="s">
+        <v>112</v>
+      </c>
+      <c r="G70" t="s">
+        <v>13</v>
+      </c>
+      <c r="H70" t="s">
         <v>300</v>
       </c>
-      <c r="E70" t="s">
-        <v>112</v>
-      </c>
-      <c r="F70" t="s">
-        <v>113</v>
-      </c>
-      <c r="G70" t="s">
-        <v>13</v>
-      </c>
-      <c r="H70" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
+        <v>302</v>
+      </c>
+      <c r="C71" t="s">
         <v>303</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
+        <v>305</v>
+      </c>
+      <c r="E71" t="s">
         <v>304</v>
       </c>
-      <c r="D71" t="s">
+      <c r="F71" t="s">
+        <v>304</v>
+      </c>
+      <c r="G71" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" t="s">
         <v>306</v>
       </c>
-      <c r="E71" t="s">
-        <v>305</v>
-      </c>
-      <c r="F71" t="s">
-        <v>305</v>
-      </c>
-      <c r="G71" t="s">
-        <v>13</v>
-      </c>
-      <c r="H71" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>307</v>
+      </c>
+      <c r="C72" t="s">
         <v>308</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>309</v>
       </c>
-      <c r="D72" t="s">
+      <c r="E72" t="s">
+        <v>304</v>
+      </c>
+      <c r="F72" t="s">
+        <v>304</v>
+      </c>
+      <c r="G72" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" t="s">
         <v>310</v>
       </c>
-      <c r="E72" t="s">
-        <v>305</v>
-      </c>
-      <c r="F72" t="s">
-        <v>305</v>
-      </c>
-      <c r="G72" t="s">
-        <v>13</v>
-      </c>
-      <c r="H72" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>311</v>
+      </c>
+      <c r="C73" t="s">
         <v>312</v>
       </c>
-      <c r="C73" t="s">
+      <c r="D73" t="s">
         <v>313</v>
       </c>
-      <c r="D73" t="s">
+      <c r="E73" t="s">
         <v>314</v>
       </c>
-      <c r="E73" t="s">
+      <c r="F73" t="s">
         <v>315</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>316</v>
       </c>
-      <c r="G73" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H73" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>317</v>
+      </c>
+      <c r="C74" t="s">
         <v>318</v>
       </c>
-      <c r="C74" t="s">
+      <c r="D74" t="s">
         <v>319</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
+        <v>304</v>
+      </c>
+      <c r="F74" t="s">
+        <v>304</v>
+      </c>
+      <c r="G74" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" t="s">
         <v>320</v>
       </c>
-      <c r="E74" t="s">
-        <v>305</v>
-      </c>
-      <c r="F74" t="s">
-        <v>305</v>
-      </c>
-      <c r="G74" t="s">
-        <v>13</v>
-      </c>
-      <c r="H74" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>321</v>
+      </c>
+      <c r="C75" t="s">
         <v>322</v>
       </c>
-      <c r="C75" t="s">
+      <c r="D75" t="s">
         <v>323</v>
       </c>
-      <c r="D75" t="s">
+      <c r="E75" t="s">
+        <v>171</v>
+      </c>
+      <c r="F75" t="s">
+        <v>12</v>
+      </c>
+      <c r="G75" t="s">
+        <v>13</v>
+      </c>
+      <c r="H75" t="s">
         <v>324</v>
       </c>
-      <c r="E75" t="s">
-        <v>172</v>
-      </c>
-      <c r="F75" t="s">
-        <v>12</v>
-      </c>
-      <c r="G75" t="s">
-        <v>13</v>
-      </c>
-      <c r="H75" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" t="s">
         <v>326</v>
       </c>
-      <c r="C76" t="s">
+      <c r="D76" t="s">
         <v>327</v>
-      </c>
-      <c r="D76" t="s">
-        <v>328</v>
       </c>
       <c r="E76" t="s">
         <v>11</v>
@@ -3905,310 +3919,310 @@
         <v>13</v>
       </c>
       <c r="H76" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
+        <v>329</v>
+      </c>
+      <c r="C77" t="s">
         <v>330</v>
       </c>
-      <c r="C77" t="s">
+      <c r="D77" t="s">
         <v>331</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E77" t="s">
+        <v>111</v>
+      </c>
+      <c r="F77" t="s">
+        <v>112</v>
+      </c>
+      <c r="G77" t="s">
+        <v>13</v>
+      </c>
+      <c r="H77" t="s">
         <v>332</v>
       </c>
-      <c r="E77" t="s">
-        <v>112</v>
-      </c>
-      <c r="F77" t="s">
-        <v>113</v>
-      </c>
-      <c r="G77" t="s">
-        <v>13</v>
-      </c>
-      <c r="H77" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
+        <v>354</v>
+      </c>
+      <c r="C78" t="s">
         <v>355</v>
       </c>
-      <c r="C78" t="s">
+      <c r="D78" t="s">
         <v>356</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E78" t="s">
+        <v>111</v>
+      </c>
+      <c r="F78" t="s">
+        <v>112</v>
+      </c>
+      <c r="G78" t="s">
+        <v>13</v>
+      </c>
+      <c r="H78" t="s">
         <v>357</v>
       </c>
-      <c r="E78" t="s">
-        <v>112</v>
-      </c>
-      <c r="F78" t="s">
-        <v>113</v>
-      </c>
-      <c r="G78" t="s">
-        <v>13</v>
-      </c>
-      <c r="H78" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>333</v>
+      </c>
+      <c r="C79" t="s">
         <v>334</v>
       </c>
-      <c r="C79" t="s">
+      <c r="D79" t="s">
         <v>335</v>
       </c>
-      <c r="D79" t="s">
+      <c r="E79" t="s">
         <v>336</v>
       </c>
-      <c r="E79" t="s">
+      <c r="F79" t="s">
+        <v>112</v>
+      </c>
+      <c r="G79" t="s">
+        <v>13</v>
+      </c>
+      <c r="H79" t="s">
         <v>337</v>
       </c>
-      <c r="F79" t="s">
-        <v>113</v>
-      </c>
-      <c r="G79" t="s">
-        <v>13</v>
-      </c>
-      <c r="H79" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>338</v>
+      </c>
+      <c r="C80" t="s">
         <v>339</v>
       </c>
-      <c r="C80" t="s">
+      <c r="D80" t="s">
         <v>340</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
+        <v>304</v>
+      </c>
+      <c r="F80" t="s">
+        <v>304</v>
+      </c>
+      <c r="G80" t="s">
+        <v>13</v>
+      </c>
+      <c r="H80" t="s">
         <v>341</v>
       </c>
-      <c r="E80" t="s">
-        <v>305</v>
-      </c>
-      <c r="F80" t="s">
-        <v>305</v>
-      </c>
-      <c r="G80" t="s">
-        <v>13</v>
-      </c>
-      <c r="H80" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>342</v>
+      </c>
+      <c r="C81" t="s">
         <v>343</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D81" t="s">
         <v>344</v>
       </c>
-      <c r="D81" t="s">
+      <c r="E81" t="s">
+        <v>304</v>
+      </c>
+      <c r="F81" t="s">
+        <v>304</v>
+      </c>
+      <c r="G81" t="s">
+        <v>13</v>
+      </c>
+      <c r="H81" t="s">
         <v>345</v>
       </c>
-      <c r="E81" t="s">
-        <v>305</v>
-      </c>
-      <c r="F81" t="s">
-        <v>305</v>
-      </c>
-      <c r="G81" t="s">
-        <v>13</v>
-      </c>
-      <c r="H81" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
+        <v>346</v>
+      </c>
+      <c r="C82" t="s">
         <v>347</v>
       </c>
-      <c r="C82" t="s">
+      <c r="D82" t="s">
         <v>348</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
+        <v>304</v>
+      </c>
+      <c r="F82" t="s">
+        <v>304</v>
+      </c>
+      <c r="G82" t="s">
+        <v>13</v>
+      </c>
+      <c r="H82" t="s">
         <v>349</v>
       </c>
-      <c r="E82" t="s">
-        <v>305</v>
-      </c>
-      <c r="F82" t="s">
-        <v>305</v>
-      </c>
-      <c r="G82" t="s">
-        <v>13</v>
-      </c>
-      <c r="H82" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
+        <v>350</v>
+      </c>
+      <c r="C83" t="s">
         <v>351</v>
       </c>
-      <c r="C83" t="s">
+      <c r="D83" t="s">
         <v>352</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
+        <v>304</v>
+      </c>
+      <c r="F83" t="s">
+        <v>304</v>
+      </c>
+      <c r="G83" t="s">
+        <v>13</v>
+      </c>
+      <c r="H83" t="s">
         <v>353</v>
       </c>
-      <c r="E83" t="s">
-        <v>305</v>
-      </c>
-      <c r="F83" t="s">
-        <v>305</v>
-      </c>
-      <c r="G83" t="s">
-        <v>13</v>
-      </c>
-      <c r="H83" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
+        <v>358</v>
+      </c>
+      <c r="C84" t="s">
         <v>359</v>
       </c>
-      <c r="C84" t="s">
+      <c r="D84" t="s">
         <v>360</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
+        <v>83</v>
+      </c>
+      <c r="F84" t="s">
+        <v>12</v>
+      </c>
+      <c r="G84" t="s">
+        <v>13</v>
+      </c>
+      <c r="H84" t="s">
         <v>361</v>
       </c>
-      <c r="E84" t="s">
-        <v>84</v>
-      </c>
-      <c r="F84" t="s">
-        <v>12</v>
-      </c>
-      <c r="G84" t="s">
-        <v>13</v>
-      </c>
-      <c r="H84" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
+        <v>362</v>
+      </c>
+      <c r="C85" t="s">
         <v>363</v>
       </c>
-      <c r="C85" t="s">
+      <c r="D85" t="s">
         <v>364</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E85" t="s">
+        <v>111</v>
+      </c>
+      <c r="F85" t="s">
+        <v>112</v>
+      </c>
+      <c r="G85" t="s">
+        <v>13</v>
+      </c>
+      <c r="H85" t="s">
         <v>365</v>
       </c>
-      <c r="E85" t="s">
-        <v>112</v>
-      </c>
-      <c r="F85" t="s">
-        <v>113</v>
-      </c>
-      <c r="G85" t="s">
-        <v>13</v>
-      </c>
-      <c r="H85" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>366</v>
+      </c>
+      <c r="C86" t="s">
         <v>367</v>
       </c>
-      <c r="C86" t="s">
+      <c r="D86" t="s">
         <v>368</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E86" t="s">
+        <v>111</v>
+      </c>
+      <c r="F86" t="s">
+        <v>112</v>
+      </c>
+      <c r="G86" t="s">
+        <v>13</v>
+      </c>
+      <c r="H86" t="s">
         <v>369</v>
       </c>
-      <c r="E86" t="s">
-        <v>112</v>
-      </c>
-      <c r="F86" t="s">
-        <v>113</v>
-      </c>
-      <c r="G86" t="s">
-        <v>13</v>
-      </c>
-      <c r="H86" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>370</v>
+      </c>
+      <c r="C87" t="s">
         <v>371</v>
       </c>
-      <c r="C87" t="s">
+      <c r="D87" t="s">
         <v>372</v>
       </c>
-      <c r="D87" t="s">
+      <c r="E87" t="s">
+        <v>83</v>
+      </c>
+      <c r="F87" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" t="s">
+        <v>13</v>
+      </c>
+      <c r="H87" t="s">
         <v>373</v>
       </c>
-      <c r="E87" t="s">
-        <v>84</v>
-      </c>
-      <c r="F87" t="s">
-        <v>12</v>
-      </c>
-      <c r="G87" t="s">
-        <v>13</v>
-      </c>
-      <c r="H87" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
+        <v>374</v>
+      </c>
+      <c r="C88" t="s">
         <v>375</v>
       </c>
-      <c r="C88" t="s">
+      <c r="D88" t="s">
         <v>376</v>
       </c>
-      <c r="D88" t="s">
-        <v>377</v>
-      </c>
       <c r="E88" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F88" t="s">
         <v>12</v>
@@ -4216,25 +4230,25 @@
       <c r="G88" t="s">
         <v>13</v>
       </c>
-      <c r="H88" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H88" s="2" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>377</v>
+      </c>
+      <c r="C89" t="s">
         <v>378</v>
       </c>
-      <c r="C89" t="s">
+      <c r="D89" t="s">
         <v>379</v>
       </c>
-      <c r="D89" t="s">
-        <v>380</v>
-      </c>
       <c r="E89" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F89" t="s">
         <v>12</v>
@@ -4242,42 +4256,48 @@
       <c r="G89" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H89" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>380</v>
+      </c>
+      <c r="C90" t="s">
         <v>381</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>382</v>
       </c>
-      <c r="D90" t="s">
-        <v>383</v>
-      </c>
       <c r="E90" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F90" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G90" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H90" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>383</v>
+      </c>
+      <c r="C91" t="s">
         <v>384</v>
       </c>
-      <c r="C91" t="s">
+      <c r="D91" t="s">
         <v>385</v>
-      </c>
-      <c r="D91" t="s">
-        <v>386</v>
       </c>
       <c r="E91" t="s">
         <v>11</v>
@@ -4289,281 +4309,281 @@
         <v>13</v>
       </c>
       <c r="H91" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
+        <v>387</v>
+      </c>
+      <c r="C92" t="s">
         <v>388</v>
       </c>
-      <c r="C92" t="s">
+      <c r="D92" t="s">
         <v>389</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
+        <v>163</v>
+      </c>
+      <c r="F92" t="s">
+        <v>12</v>
+      </c>
+      <c r="G92" t="s">
+        <v>13</v>
+      </c>
+      <c r="H92" t="s">
         <v>390</v>
       </c>
-      <c r="E92" t="s">
-        <v>164</v>
-      </c>
-      <c r="F92" t="s">
-        <v>12</v>
-      </c>
-      <c r="G92" t="s">
-        <v>13</v>
-      </c>
-      <c r="H92" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
+        <v>391</v>
+      </c>
+      <c r="C93" t="s">
         <v>392</v>
       </c>
-      <c r="C93" t="s">
+      <c r="D93" t="s">
         <v>393</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
+        <v>115</v>
+      </c>
+      <c r="F93" t="s">
+        <v>12</v>
+      </c>
+      <c r="G93" t="s">
+        <v>13</v>
+      </c>
+      <c r="H93" t="s">
         <v>394</v>
       </c>
-      <c r="E93" t="s">
-        <v>116</v>
-      </c>
-      <c r="F93" t="s">
-        <v>12</v>
-      </c>
-      <c r="G93" t="s">
-        <v>13</v>
-      </c>
-      <c r="H93" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
+        <v>395</v>
+      </c>
+      <c r="C94" t="s">
         <v>396</v>
       </c>
-      <c r="C94" t="s">
+      <c r="D94" t="s">
         <v>397</v>
       </c>
-      <c r="D94" t="s">
+      <c r="E94" t="s">
+        <v>115</v>
+      </c>
+      <c r="F94" t="s">
+        <v>12</v>
+      </c>
+      <c r="G94" t="s">
+        <v>13</v>
+      </c>
+      <c r="H94" t="s">
         <v>398</v>
       </c>
-      <c r="E94" t="s">
-        <v>116</v>
-      </c>
-      <c r="F94" t="s">
-        <v>12</v>
-      </c>
-      <c r="G94" t="s">
-        <v>13</v>
-      </c>
-      <c r="H94" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
+        <v>399</v>
+      </c>
+      <c r="C95" t="s">
         <v>400</v>
       </c>
-      <c r="C95" t="s">
+      <c r="D95" t="s">
         <v>401</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
+        <v>105</v>
+      </c>
+      <c r="F95" t="s">
+        <v>12</v>
+      </c>
+      <c r="G95" t="s">
+        <v>13</v>
+      </c>
+      <c r="H95" t="s">
         <v>402</v>
       </c>
-      <c r="E95" t="s">
-        <v>106</v>
-      </c>
-      <c r="F95" t="s">
-        <v>12</v>
-      </c>
-      <c r="G95" t="s">
-        <v>13</v>
-      </c>
-      <c r="H95" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
+        <v>403</v>
+      </c>
+      <c r="C96" t="s">
         <v>404</v>
       </c>
-      <c r="C96" t="s">
+      <c r="D96" t="s">
         <v>405</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
+        <v>135</v>
+      </c>
+      <c r="F96" t="s">
+        <v>12</v>
+      </c>
+      <c r="G96" t="s">
+        <v>13</v>
+      </c>
+      <c r="H96" t="s">
         <v>406</v>
       </c>
-      <c r="E96" t="s">
-        <v>136</v>
-      </c>
-      <c r="F96" t="s">
-        <v>12</v>
-      </c>
-      <c r="G96" t="s">
-        <v>13</v>
-      </c>
-      <c r="H96" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
+        <v>407</v>
+      </c>
+      <c r="C97" t="s">
         <v>408</v>
       </c>
-      <c r="C97" t="s">
+      <c r="D97" t="s">
+        <v>301</v>
+      </c>
+      <c r="E97" t="s">
+        <v>83</v>
+      </c>
+      <c r="F97" t="s">
+        <v>12</v>
+      </c>
+      <c r="G97" t="s">
+        <v>13</v>
+      </c>
+      <c r="H97" t="s">
         <v>409</v>
       </c>
-      <c r="D97" t="s">
-        <v>302</v>
-      </c>
-      <c r="E97" t="s">
-        <v>84</v>
-      </c>
-      <c r="F97" t="s">
-        <v>12</v>
-      </c>
-      <c r="G97" t="s">
-        <v>13</v>
-      </c>
-      <c r="H97" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>410</v>
+      </c>
+      <c r="C98" t="s">
         <v>411</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
         <v>412</v>
       </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
+        <v>83</v>
+      </c>
+      <c r="F98" t="s">
+        <v>12</v>
+      </c>
+      <c r="G98" t="s">
+        <v>13</v>
+      </c>
+      <c r="H98" t="s">
         <v>413</v>
       </c>
-      <c r="E98" t="s">
-        <v>84</v>
-      </c>
-      <c r="F98" t="s">
-        <v>12</v>
-      </c>
-      <c r="G98" t="s">
-        <v>13</v>
-      </c>
-      <c r="H98" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
       <c r="B99" t="s">
+        <v>414</v>
+      </c>
+      <c r="C99" t="s">
         <v>415</v>
       </c>
-      <c r="C99" t="s">
+      <c r="D99" t="s">
         <v>416</v>
       </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
+        <v>115</v>
+      </c>
+      <c r="F99" t="s">
+        <v>12</v>
+      </c>
+      <c r="G99" t="s">
+        <v>13</v>
+      </c>
+      <c r="H99" t="s">
         <v>417</v>
       </c>
-      <c r="E99" t="s">
-        <v>116</v>
-      </c>
-      <c r="F99" t="s">
-        <v>12</v>
-      </c>
-      <c r="G99" t="s">
-        <v>13</v>
-      </c>
-      <c r="H99" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>418</v>
+      </c>
+      <c r="C100" t="s">
         <v>419</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>420</v>
       </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
+        <v>279</v>
+      </c>
+      <c r="F100" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" t="s">
+        <v>13</v>
+      </c>
+      <c r="H100" t="s">
         <v>421</v>
       </c>
-      <c r="E100" t="s">
-        <v>280</v>
-      </c>
-      <c r="F100" t="s">
-        <v>12</v>
-      </c>
-      <c r="G100" t="s">
-        <v>13</v>
-      </c>
-      <c r="H100" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>422</v>
+      </c>
+      <c r="C101" t="s">
         <v>423</v>
       </c>
-      <c r="C101" t="s">
+      <c r="D101" t="s">
         <v>424</v>
       </c>
-      <c r="D101" t="s">
+      <c r="E101" t="s">
+        <v>83</v>
+      </c>
+      <c r="F101" t="s">
+        <v>12</v>
+      </c>
+      <c r="G101" t="s">
+        <v>13</v>
+      </c>
+      <c r="H101" t="s">
         <v>425</v>
       </c>
-      <c r="E101" t="s">
-        <v>84</v>
-      </c>
-      <c r="F101" t="s">
-        <v>12</v>
-      </c>
-      <c r="G101" t="s">
-        <v>13</v>
-      </c>
-      <c r="H101" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
       <c r="B102" t="s">
+        <v>426</v>
+      </c>
+      <c r="C102" t="s">
         <v>427</v>
       </c>
-      <c r="C102" t="s">
+      <c r="D102" t="s">
         <v>428</v>
-      </c>
-      <c r="D102" t="s">
-        <v>429</v>
       </c>
       <c r="E102" t="s">
         <v>11</v>
@@ -4575,258 +4595,258 @@
         <v>13</v>
       </c>
       <c r="H102" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
       <c r="B103" t="s">
+        <v>430</v>
+      </c>
+      <c r="C103" t="s">
         <v>431</v>
       </c>
-      <c r="C103" t="s">
+      <c r="D103" t="s">
         <v>432</v>
       </c>
-      <c r="D103" t="s">
+      <c r="E103" t="s">
+        <v>111</v>
+      </c>
+      <c r="F103" t="s">
+        <v>112</v>
+      </c>
+      <c r="G103" t="s">
+        <v>13</v>
+      </c>
+      <c r="H103" t="s">
         <v>433</v>
       </c>
-      <c r="E103" t="s">
-        <v>112</v>
-      </c>
-      <c r="F103" t="s">
-        <v>113</v>
-      </c>
-      <c r="G103" t="s">
-        <v>13</v>
-      </c>
-      <c r="H103" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
       <c r="B104" t="s">
+        <v>434</v>
+      </c>
+      <c r="C104" t="s">
         <v>435</v>
       </c>
-      <c r="C104" t="s">
+      <c r="D104" t="s">
         <v>436</v>
       </c>
-      <c r="D104" t="s">
+      <c r="E104" t="s">
+        <v>111</v>
+      </c>
+      <c r="F104" t="s">
+        <v>112</v>
+      </c>
+      <c r="G104" t="s">
+        <v>13</v>
+      </c>
+      <c r="H104" t="s">
         <v>437</v>
       </c>
-      <c r="E104" t="s">
-        <v>112</v>
-      </c>
-      <c r="F104" t="s">
-        <v>113</v>
-      </c>
-      <c r="G104" t="s">
-        <v>13</v>
-      </c>
-      <c r="H104" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
       <c r="B105" t="s">
+        <v>457</v>
+      </c>
+      <c r="C105" t="s">
         <v>458</v>
       </c>
-      <c r="C105" t="s">
+      <c r="D105" t="s">
         <v>459</v>
       </c>
-      <c r="D105" t="s">
+      <c r="E105" t="s">
+        <v>449</v>
+      </c>
+      <c r="F105" t="s">
+        <v>450</v>
+      </c>
+      <c r="G105" t="s">
+        <v>13</v>
+      </c>
+      <c r="H105" t="s">
         <v>460</v>
       </c>
-      <c r="E105" t="s">
-        <v>450</v>
-      </c>
-      <c r="F105" t="s">
-        <v>451</v>
-      </c>
-      <c r="G105" t="s">
-        <v>13</v>
-      </c>
-      <c r="H105" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>438</v>
+      </c>
+      <c r="C106" t="s">
         <v>439</v>
       </c>
-      <c r="C106" t="s">
+      <c r="D106" t="s">
         <v>440</v>
       </c>
-      <c r="D106" t="s">
+      <c r="E106" t="s">
+        <v>135</v>
+      </c>
+      <c r="F106" t="s">
+        <v>12</v>
+      </c>
+      <c r="G106" t="s">
+        <v>13</v>
+      </c>
+      <c r="H106" t="s">
         <v>441</v>
       </c>
-      <c r="E106" t="s">
-        <v>136</v>
-      </c>
-      <c r="F106" t="s">
-        <v>12</v>
-      </c>
-      <c r="G106" t="s">
-        <v>13</v>
-      </c>
-      <c r="H106" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
       <c r="B107" t="s">
+        <v>442</v>
+      </c>
+      <c r="C107" t="s">
         <v>443</v>
       </c>
-      <c r="C107" t="s">
+      <c r="D107" t="s">
         <v>444</v>
       </c>
-      <c r="D107" t="s">
+      <c r="E107" t="s">
+        <v>111</v>
+      </c>
+      <c r="F107" t="s">
+        <v>112</v>
+      </c>
+      <c r="G107" t="s">
+        <v>13</v>
+      </c>
+      <c r="H107" t="s">
         <v>445</v>
       </c>
-      <c r="E107" t="s">
-        <v>112</v>
-      </c>
-      <c r="F107" t="s">
-        <v>113</v>
-      </c>
-      <c r="G107" t="s">
-        <v>13</v>
-      </c>
-      <c r="H107" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>446</v>
+      </c>
+      <c r="C108" t="s">
         <v>447</v>
       </c>
-      <c r="C108" t="s">
+      <c r="D108" t="s">
         <v>448</v>
       </c>
-      <c r="D108" t="s">
+      <c r="E108" t="s">
         <v>449</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>450</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
+        <v>13</v>
+      </c>
+      <c r="H108" t="s">
         <v>451</v>
       </c>
-      <c r="G108" t="s">
-        <v>13</v>
-      </c>
-      <c r="H108" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
       <c r="B109" t="s">
+        <v>452</v>
+      </c>
+      <c r="C109" t="s">
         <v>453</v>
       </c>
-      <c r="C109" t="s">
+      <c r="D109" t="s">
         <v>454</v>
       </c>
-      <c r="D109" t="s">
+      <c r="E109" t="s">
         <v>455</v>
       </c>
-      <c r="E109" t="s">
+      <c r="F109" t="s">
+        <v>112</v>
+      </c>
+      <c r="G109" t="s">
+        <v>13</v>
+      </c>
+      <c r="H109" t="s">
         <v>456</v>
       </c>
-      <c r="F109" t="s">
-        <v>113</v>
-      </c>
-      <c r="G109" t="s">
-        <v>13</v>
-      </c>
-      <c r="H109" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>461</v>
+      </c>
+      <c r="C110" t="s">
         <v>462</v>
       </c>
-      <c r="C110" t="s">
+      <c r="D110" t="s">
         <v>463</v>
       </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
+        <v>304</v>
+      </c>
+      <c r="F110" t="s">
+        <v>304</v>
+      </c>
+      <c r="G110" t="s">
+        <v>13</v>
+      </c>
+      <c r="H110" t="s">
         <v>464</v>
       </c>
-      <c r="E110" t="s">
-        <v>305</v>
-      </c>
-      <c r="F110" t="s">
-        <v>305</v>
-      </c>
-      <c r="G110" t="s">
-        <v>13</v>
-      </c>
-      <c r="H110" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
       <c r="B111" t="s">
+        <v>465</v>
+      </c>
+      <c r="C111" t="s">
         <v>466</v>
       </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
         <v>467</v>
       </c>
-      <c r="D111" t="s">
+      <c r="E111" t="s">
+        <v>163</v>
+      </c>
+      <c r="F111" t="s">
+        <v>12</v>
+      </c>
+      <c r="G111" t="s">
+        <v>13</v>
+      </c>
+      <c r="H111" t="s">
         <v>468</v>
       </c>
-      <c r="E111" t="s">
-        <v>164</v>
-      </c>
-      <c r="F111" t="s">
-        <v>12</v>
-      </c>
-      <c r="G111" t="s">
-        <v>13</v>
-      </c>
-      <c r="H111" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
       <c r="B112" t="s">
+        <v>469</v>
+      </c>
+      <c r="C112" t="s">
         <v>470</v>
       </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
         <v>471</v>
       </c>
-      <c r="D112" t="s">
-        <v>472</v>
-      </c>
       <c r="E112" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F112" t="s">
         <v>12</v>
@@ -4834,256 +4854,256 @@
       <c r="G112" t="s">
         <v>13</v>
       </c>
-      <c r="H112" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="H112" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
       <c r="B113" t="s">
+        <v>472</v>
+      </c>
+      <c r="C113" t="s">
         <v>473</v>
       </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
         <v>474</v>
       </c>
-      <c r="D113" t="s">
+      <c r="E113" t="s">
+        <v>130</v>
+      </c>
+      <c r="F113" t="s">
+        <v>12</v>
+      </c>
+      <c r="G113" t="s">
+        <v>13</v>
+      </c>
+      <c r="H113" t="s">
         <v>475</v>
       </c>
-      <c r="E113" t="s">
-        <v>131</v>
-      </c>
-      <c r="F113" t="s">
-        <v>12</v>
-      </c>
-      <c r="G113" t="s">
-        <v>13</v>
-      </c>
-      <c r="H113" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
       <c r="B114" t="s">
+        <v>476</v>
+      </c>
+      <c r="C114" t="s">
         <v>477</v>
       </c>
-      <c r="C114" t="s">
+      <c r="D114" t="s">
         <v>478</v>
       </c>
-      <c r="D114" t="s">
+      <c r="E114" t="s">
         <v>479</v>
       </c>
-      <c r="E114" t="s">
+      <c r="F114" t="s">
         <v>480</v>
       </c>
-      <c r="F114" t="s">
+      <c r="G114" t="s">
+        <v>13</v>
+      </c>
+      <c r="H114" t="s">
         <v>481</v>
       </c>
-      <c r="G114" t="s">
-        <v>13</v>
-      </c>
-      <c r="H114" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
       <c r="B115" t="s">
+        <v>482</v>
+      </c>
+      <c r="C115" t="s">
         <v>483</v>
       </c>
-      <c r="C115" t="s">
+      <c r="D115" t="s">
         <v>484</v>
       </c>
-      <c r="D115" t="s">
+      <c r="E115" t="s">
+        <v>83</v>
+      </c>
+      <c r="F115" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" t="s">
+        <v>13</v>
+      </c>
+      <c r="H115" t="s">
         <v>485</v>
       </c>
-      <c r="E115" t="s">
-        <v>84</v>
-      </c>
-      <c r="F115" t="s">
-        <v>12</v>
-      </c>
-      <c r="G115" t="s">
-        <v>13</v>
-      </c>
-      <c r="H115" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
       <c r="B116" t="s">
+        <v>486</v>
+      </c>
+      <c r="C116" t="s">
         <v>487</v>
       </c>
-      <c r="C116" t="s">
+      <c r="D116" t="s">
         <v>488</v>
       </c>
-      <c r="D116" t="s">
+      <c r="E116" t="s">
+        <v>83</v>
+      </c>
+      <c r="F116" t="s">
+        <v>12</v>
+      </c>
+      <c r="G116" t="s">
+        <v>13</v>
+      </c>
+      <c r="H116" t="s">
         <v>489</v>
       </c>
-      <c r="E116" t="s">
-        <v>84</v>
-      </c>
-      <c r="F116" t="s">
-        <v>12</v>
-      </c>
-      <c r="G116" t="s">
-        <v>13</v>
-      </c>
-      <c r="H116" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
       <c r="B117" t="s">
+        <v>490</v>
+      </c>
+      <c r="C117" t="s">
         <v>491</v>
       </c>
-      <c r="C117" t="s">
+      <c r="D117" t="s">
         <v>492</v>
       </c>
-      <c r="D117" t="s">
+      <c r="E117" t="s">
+        <v>105</v>
+      </c>
+      <c r="F117" t="s">
+        <v>12</v>
+      </c>
+      <c r="G117" t="s">
+        <v>13</v>
+      </c>
+      <c r="H117" t="s">
         <v>493</v>
       </c>
-      <c r="E117" t="s">
-        <v>106</v>
-      </c>
-      <c r="F117" t="s">
-        <v>12</v>
-      </c>
-      <c r="G117" t="s">
-        <v>13</v>
-      </c>
-      <c r="H117" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
       <c r="B118" t="s">
+        <v>494</v>
+      </c>
+      <c r="C118" t="s">
         <v>495</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" t="s">
         <v>496</v>
       </c>
-      <c r="D118" t="s">
+      <c r="E118" t="s">
+        <v>83</v>
+      </c>
+      <c r="F118" t="s">
+        <v>12</v>
+      </c>
+      <c r="G118" t="s">
+        <v>13</v>
+      </c>
+      <c r="H118" t="s">
         <v>497</v>
       </c>
-      <c r="E118" t="s">
-        <v>84</v>
-      </c>
-      <c r="F118" t="s">
-        <v>12</v>
-      </c>
-      <c r="G118" t="s">
-        <v>13</v>
-      </c>
-      <c r="H118" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
       <c r="B119" t="s">
+        <v>498</v>
+      </c>
+      <c r="C119" t="s">
         <v>499</v>
       </c>
-      <c r="C119" t="s">
+      <c r="D119" t="s">
         <v>500</v>
       </c>
-      <c r="D119" t="s">
+      <c r="E119" t="s">
+        <v>163</v>
+      </c>
+      <c r="F119" t="s">
+        <v>12</v>
+      </c>
+      <c r="G119" t="s">
+        <v>13</v>
+      </c>
+      <c r="H119" t="s">
         <v>501</v>
       </c>
-      <c r="E119" t="s">
-        <v>164</v>
-      </c>
-      <c r="F119" t="s">
-        <v>12</v>
-      </c>
-      <c r="G119" t="s">
-        <v>13</v>
-      </c>
-      <c r="H119" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
       <c r="B120" t="s">
+        <v>502</v>
+      </c>
+      <c r="C120" t="s">
         <v>503</v>
       </c>
-      <c r="C120" t="s">
+      <c r="D120" t="s">
         <v>504</v>
       </c>
-      <c r="D120" t="s">
+      <c r="E120" t="s">
+        <v>115</v>
+      </c>
+      <c r="F120" t="s">
+        <v>12</v>
+      </c>
+      <c r="G120" t="s">
+        <v>13</v>
+      </c>
+      <c r="H120" t="s">
         <v>505</v>
       </c>
-      <c r="E120" t="s">
-        <v>116</v>
-      </c>
-      <c r="F120" t="s">
-        <v>12</v>
-      </c>
-      <c r="G120" t="s">
-        <v>13</v>
-      </c>
-      <c r="H120" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
       <c r="B121" t="s">
+        <v>506</v>
+      </c>
+      <c r="C121" t="s">
         <v>507</v>
       </c>
-      <c r="C121" t="s">
+      <c r="D121" t="s">
         <v>508</v>
       </c>
-      <c r="D121" t="s">
+      <c r="E121" t="s">
+        <v>83</v>
+      </c>
+      <c r="F121" t="s">
+        <v>12</v>
+      </c>
+      <c r="G121" t="s">
+        <v>13</v>
+      </c>
+      <c r="H121" t="s">
         <v>509</v>
       </c>
-      <c r="E121" t="s">
-        <v>84</v>
-      </c>
-      <c r="F121" t="s">
-        <v>12</v>
-      </c>
-      <c r="G121" t="s">
-        <v>13</v>
-      </c>
-      <c r="H121" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
       <c r="B122" t="s">
+        <v>510</v>
+      </c>
+      <c r="C122" t="s">
         <v>511</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
         <v>512</v>
-      </c>
-      <c r="D122" t="s">
-        <v>513</v>
       </c>
       <c r="E122" t="s">
         <v>11</v>
@@ -5095,15 +5115,23 @@
         <v>13</v>
       </c>
       <c r="H122" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H122">
+    <sortState ref="A2:H122">
       <sortCondition ref="B1"/>
     </sortState>
   </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="H43" r:id="rId1" xr:uid="{40B348CE-0B34-422B-AB74-AC333C69883A}"/>
+    <hyperlink ref="H112" r:id="rId2" xr:uid="{3056BBB8-D581-4C16-B50F-84267EA52381}"/>
+    <hyperlink ref="H73" r:id="rId3" xr:uid="{255A7CDD-5E68-4B91-9F67-0E5C9765B2FC}"/>
+    <hyperlink ref="H88" r:id="rId4" xr:uid="{B682E321-732F-48D1-AA11-69E7B9322414}"/>
+    <hyperlink ref="H89" r:id="rId5" xr:uid="{1CCF72B4-043B-47EF-AA2C-0498673FF81F}"/>
+    <hyperlink ref="H90" r:id="rId6" xr:uid="{E78A4431-5D1E-4172-A1F0-2CA641E0291D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>